--- a/Output/Tables/Table_div10_adjusted_malf.xlsx
+++ b/Output/Tables/Table_div10_adjusted_malf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/estela_blanco_uc_cl/Documents/Contaminación_Malformaciones Congénitas/Pollution_Malformation_TEM/Output/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_286D261F301DF2CBA494564DA7DC1B50797E0434" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3788AA5-7630-D24C-9EC9-6032D50BD26E}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_0F4C20D3AB161FACD045CE38DFDEBD12F631295C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CDCD5A8-D925-6645-801A-F4D8C700B1CB}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="84">
   <si>
     <t>Section</t>
   </si>
@@ -58,13 +58,13 @@
     <t>Trimester 1</t>
   </si>
   <si>
-    <t>0.94 (0.83, 1.06)</t>
-  </si>
-  <si>
-    <t>0.69 (0.32, 1.52)</t>
-  </si>
-  <si>
-    <t>0.69 (0.34, 1.40)</t>
+    <t>0.93 (0.82, 1.05)</t>
+  </si>
+  <si>
+    <t>0.64 (0.29, 1.39)</t>
+  </si>
+  <si>
+    <t>0.66 (0.33, 1.32)</t>
   </si>
   <si>
     <t>Trimester 2</t>
@@ -73,22 +73,22 @@
     <t>1.07 (0.94, 1.22)</t>
   </si>
   <si>
-    <t>1.51 (0.68, 3.37)</t>
-  </si>
-  <si>
-    <t>1.45 (0.69, 3.04)</t>
+    <t>1.58 (0.69, 3.58)</t>
+  </si>
+  <si>
+    <t>1.47 (0.70, 3.12)</t>
   </si>
   <si>
     <t>Trimester 3</t>
   </si>
   <si>
-    <t>1.05 (0.92, 1.18)</t>
-  </si>
-  <si>
-    <t>1.25 (0.58, 2.70)</t>
-  </si>
-  <si>
-    <t>1.28 (0.63, 2.57)</t>
+    <t>1.04 (0.91, 1.17)</t>
+  </si>
+  <si>
+    <t>1.16 (0.53, 2.52)</t>
+  </si>
+  <si>
+    <t>1.19 (0.59, 2.43)</t>
   </si>
   <si>
     <t>Land-use regression (sp)</t>
@@ -103,154 +103,157 @@
     <t>0.61 (0.40, 0.92)</t>
   </si>
   <si>
-    <t>0.96 (0.90, 1.01)</t>
-  </si>
-  <si>
-    <t>0.82 (0.42, 1.61)</t>
-  </si>
-  <si>
-    <t>0.74 (0.49, 1.11)</t>
+    <t>0.95 (0.90, 1.01)</t>
+  </si>
+  <si>
+    <t>0.77 (0.39, 1.52)</t>
+  </si>
+  <si>
+    <t>0.72 (0.48, 1.09)</t>
   </si>
   <si>
     <t>0.99 (0.93, 1.04)</t>
   </si>
   <si>
-    <t>1.26 (0.63, 2.51)</t>
-  </si>
-  <si>
-    <t>0.94 (0.62, 1.43)</t>
+    <t>1.30 (0.65, 2.61)</t>
+  </si>
+  <si>
+    <t>0.94 (0.62, 1.44)</t>
   </si>
   <si>
     <t>0.96 (0.91, 1.02)</t>
   </si>
   <si>
-    <t>0.89 (0.46, 1.74)</t>
-  </si>
-  <si>
-    <t>0.83 (0.55, 1.25)</t>
-  </si>
-  <si>
-    <t>0.93 (0.77, 1.11)</t>
-  </si>
-  <si>
-    <t>0.62 (0.19, 2.05)</t>
-  </si>
-  <si>
-    <t>0.66 (0.23, 1.84)</t>
+    <t>0.87 (0.44, 1.70)</t>
+  </si>
+  <si>
+    <t>0.81 (0.54, 1.22)</t>
+  </si>
+  <si>
+    <t>0.91 (0.77, 1.09)</t>
+  </si>
+  <si>
+    <t>0.52 (0.17, 1.63)</t>
+  </si>
+  <si>
+    <t>0.59 (0.22, 1.57)</t>
   </si>
   <si>
     <t>1.06 (0.93, 1.22)</t>
   </si>
   <si>
-    <t>1.48 (0.64, 3.42)</t>
-  </si>
-  <si>
-    <t>1.41 (0.65, 3.06)</t>
-  </si>
-  <si>
-    <t>0.99 (0.83, 1.20)</t>
-  </si>
-  <si>
-    <t>0.93 (0.29, 2.96)</t>
-  </si>
-  <si>
-    <t>0.98 (0.35, 2.74)</t>
+    <t>1.50 (0.64, 3.50)</t>
+  </si>
+  <si>
+    <t>1.41 (0.65, 3.07)</t>
+  </si>
+  <si>
+    <t>0.98 (0.81, 1.17)</t>
+  </si>
+  <si>
+    <t>0.76 (0.24, 2.43)</t>
+  </si>
+  <si>
+    <t>0.86 (0.31, 2.38)</t>
   </si>
   <si>
     <t>0.94 (0.88, 1.00)</t>
   </si>
   <si>
-    <t>0.61 (0.27, 1.36)</t>
-  </si>
-  <si>
-    <t>0.64 (0.40, 1.00)</t>
+    <t>0.59 (0.27, 1.31)</t>
+  </si>
+  <si>
+    <t>0.63 (0.40, 0.99)</t>
   </si>
   <si>
     <t>1.03 (0.96, 1.10)</t>
   </si>
   <si>
-    <t>1.35 (0.67, 2.71)</t>
-  </si>
-  <si>
-    <t>1.13 (0.72, 1.76)</t>
-  </si>
-  <si>
-    <t>0.94 (0.89, 1.01)</t>
-  </si>
-  <si>
-    <t>0.68 (0.31, 1.50)</t>
-  </si>
-  <si>
-    <t>0.71 (0.45, 1.11)</t>
-  </si>
-  <si>
-    <t>0.89 (0.72, 1.10)</t>
-  </si>
-  <si>
-    <t>0.41 (0.10, 1.74)</t>
-  </si>
-  <si>
-    <t>0.42 (0.12, 1.43)</t>
-  </si>
-  <si>
-    <t>0.90 (0.74, 1.08)</t>
-  </si>
-  <si>
-    <t>0.45 (0.12, 1.65)</t>
-  </si>
-  <si>
-    <t>0.48 (0.16, 1.47)</t>
-  </si>
-  <si>
-    <t>0.96 (0.76, 1.21)</t>
-  </si>
-  <si>
-    <t>0.67 (0.14, 3.10)</t>
-  </si>
-  <si>
-    <t>0.65 (0.17, 2.47)</t>
-  </si>
-  <si>
-    <t>0.96 (0.79, 1.16)</t>
-  </si>
-  <si>
-    <t>0.65 (0.18, 2.38)</t>
-  </si>
-  <si>
-    <t>0.70 (0.22, 2.17)</t>
+    <t>1.41 (0.69, 2.87)</t>
+  </si>
+  <si>
+    <t>1.15 (0.73, 1.80)</t>
+  </si>
+  <si>
+    <t>0.95 (0.89, 1.01)</t>
+  </si>
+  <si>
+    <t>0.65 (0.29, 1.45)</t>
+  </si>
+  <si>
+    <t>0.69 (0.44, 1.09)</t>
+  </si>
+  <si>
+    <t>0.88 (0.72, 1.09)</t>
+  </si>
+  <si>
+    <t>0.40 (0.10, 1.64)</t>
+  </si>
+  <si>
+    <t>0.40 (0.12, 1.32)</t>
+  </si>
+  <si>
+    <t>0.89 (0.74, 1.06)</t>
+  </si>
+  <si>
+    <t>0.39 (0.11, 1.32)</t>
+  </si>
+  <si>
+    <t>0.44 (0.15, 1.26)</t>
+  </si>
+  <si>
+    <t>0.95 (0.76, 1.19)</t>
+  </si>
+  <si>
+    <t>0.67 (0.15, 3.00)</t>
+  </si>
+  <si>
+    <t>0.63 (0.17, 2.31)</t>
+  </si>
+  <si>
+    <t>0.93 (0.76, 1.14)</t>
+  </si>
+  <si>
+    <t>0.49 (0.13, 1.89)</t>
+  </si>
+  <si>
+    <t>0.56 (0.17, 1.80)</t>
   </si>
   <si>
     <t>0.96 (0.89, 1.04)</t>
   </si>
   <si>
-    <t>0.72 (0.30, 1.74)</t>
-  </si>
-  <si>
-    <t>0.65 (0.38, 1.10)</t>
-  </si>
-  <si>
-    <t>0.68 (0.29, 1.61)</t>
-  </si>
-  <si>
-    <t>0.79 (0.47, 1.35)</t>
+    <t>0.76 (0.32, 1.78)</t>
+  </si>
+  <si>
+    <t>0.66 (0.39, 1.11)</t>
+  </si>
+  <si>
+    <t>0.97 (0.89, 1.05)</t>
+  </si>
+  <si>
+    <t>0.66 (0.28, 1.54)</t>
+  </si>
+  <si>
+    <t>0.79 (0.47, 1.32)</t>
   </si>
   <si>
     <t>1.01 (0.93, 1.09)</t>
   </si>
   <si>
-    <t>1.11 (0.46, 2.67)</t>
-  </si>
-  <si>
-    <t>0.90 (0.53, 1.52)</t>
-  </si>
-  <si>
-    <t>0.97 (0.90, 1.05)</t>
-  </si>
-  <si>
-    <t>0.75 (0.32, 1.73)</t>
-  </si>
-  <si>
-    <t>0.87 (0.52, 1.46)</t>
+    <t>1.19 (0.49, 2.87)</t>
+  </si>
+  <si>
+    <t>0.93 (0.55, 1.57)</t>
+  </si>
+  <si>
+    <t>0.97 (0.90, 1.04)</t>
+  </si>
+  <si>
+    <t>0.70 (0.31, 1.59)</t>
+  </si>
+  <si>
+    <t>0.82 (0.50, 1.36)</t>
   </si>
   <si>
     <t>Sheet</t>
@@ -626,6 +629,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1039,13 +1047,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1056,13 +1064,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1073,13 +1081,13 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1094,34 +1102,34 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
         <v>82</v>
-      </c>
-      <c r="B4" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
